--- a/public/exports-from-60/29189714.xlsx
+++ b/public/exports-from-60/29189714.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -6514,7 +6514,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t xml:space="preserve">200054009</t>
+          <t xml:space="preserve">200054021</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -9739,7 +9739,7 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t xml:space="preserve">311240209</t>
+          <t xml:space="preserve">311240221</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -13489,12 +13489,12 @@
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t xml:space="preserve">311283771</t>
+          <t xml:space="preserve">311283772</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t xml:space="preserve">AURA Rådgivning A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M180" t="inlineStr">
@@ -13564,12 +13564,12 @@
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t xml:space="preserve">311283775</t>
+          <t xml:space="preserve">311283779</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t xml:space="preserve">AURA Rådgivning A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M181" t="inlineStr">

--- a/public/exports-from-60/29189714.xlsx
+++ b/public/exports-from-60/29189714.xlsx
@@ -6514,7 +6514,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t xml:space="preserve">200054021</t>
+          <t xml:space="preserve">200054009</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -6889,7 +6889,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t xml:space="preserve">310023290</t>
+          <t xml:space="preserve">310023291</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -6964,7 +6964,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t xml:space="preserve">310023290</t>
+          <t xml:space="preserve">310023291</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -8329,12 +8329,12 @@
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -8404,12 +8404,12 @@
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -8479,12 +8479,12 @@
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -8554,12 +8554,12 @@
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -8629,12 +8629,12 @@
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -8704,12 +8704,12 @@
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -13414,12 +13414,12 @@
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t xml:space="preserve">311283766</t>
+          <t xml:space="preserve">311283768</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t xml:space="preserve">AURA Rådgivning A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M179" t="inlineStr">
@@ -13489,12 +13489,12 @@
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t xml:space="preserve">311283772</t>
+          <t xml:space="preserve">311283771</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">AURA Rådgivning A/S</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
@@ -13564,7 +13564,7 @@
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t xml:space="preserve">311283779</t>
+          <t xml:space="preserve">311283776</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">

--- a/public/exports-from-60/29189714.xlsx
+++ b/public/exports-from-60/29189714.xlsx
@@ -6889,7 +6889,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t xml:space="preserve">310023291</t>
+          <t xml:space="preserve">310023290</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -6964,7 +6964,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t xml:space="preserve">310023291</t>
+          <t xml:space="preserve">310023290</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -9739,7 +9739,7 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t xml:space="preserve">311240221</t>
+          <t xml:space="preserve">311240209</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -13489,12 +13489,12 @@
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t xml:space="preserve">311283771</t>
+          <t xml:space="preserve">311283774</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t xml:space="preserve">AURA Rådgivning A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M180" t="inlineStr">
@@ -13564,12 +13564,12 @@
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t xml:space="preserve">311283776</t>
+          <t xml:space="preserve">311283775</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">AURA Rådgivning A/S</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
